--- a/mapping/impix/s1/S1_원천인벤토리_IMPIX.xlsx
+++ b/mapping/impix/s1/S1_원천인벤토리_IMPIX.xlsx
@@ -531,7 +531,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22 14:44</t>
+          <t>2026-10-22 17:46</t>
         </is>
       </c>
     </row>
@@ -3781,12 +3781,12 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>OperationEnd</t>
+          <t>OperationEnd, ProductionPerformanceEquipment</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>SC02, SC05</t>
+          <t>SC02, SC04, SC05</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3814,7 +3814,11 @@
       <c r="Q44" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="R44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>설비활용실적은 완공(설비별)에서 파생</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -69140,7 +69144,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>ItemMaster, Operation, Equipment, Personnel, Line, RoutingLine, BOMHeader</t>
+          <t>ItemMaster, Operation, Equipment, Personnel, Line, RoutingLine, BOMHeader, ProductIncoming, ProductionPlanning, StockerInventory, StandardCost*</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -69159,7 +69163,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>착공·완공 식별자 없음 → trk_in_id 사용. LOT 계보는 tb_lot_link. 생산실적 단위(일 집계 vs 건) 결정 필요</t>
+          <t>착공·완공 식별자 없음 → trk_in_id 사용. LOT 계보는 tb_lot_link. 생산실적 단위(일 집계 vs 건) 결정 필요. KPI(PR01·PR02·SC03): ERP 생산입고와 MES 완공 대사 필요, 재공(WIP)은 현재 상태만 있어 일별 스냅샷 적재 필요, 재공 금액에 표준원가 Extension 필요</t>
         </is>
       </c>
     </row>
@@ -69215,20 +69219,21 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Equipment, Lot, Operation</t>
+          <t>Equipment, Lot, Operation, OperationStart, OperationEnd, RoutingLine, ProductionPerformanceEquipment</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
           <t>mes.tb_alarm
 mes.tb_eqp_stat
+mes.tb_trk_out
 mes.tm_code
 mes.tm_eqp</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>원천은 구간 이력, 표준은 상태 변경 이벤트 → 시작 시점 이벤트로 변환. 제어·운영 모드 코드 대응 필요</t>
+          <t>원천은 구간 이력, 표준은 상태 변경 이벤트 → 시작 시점 이벤트로 변환. 제어·운영 모드 코드 대응 필요. KPI(EQ01~EQ08): 시간가동율·MTBF·MTTR은 상태 구간을 재구성해 산출, 성능가동율·UPM은 라우팅 표준시간(RoutingLine.RunTime)과 완공 수량으로 산출. 설비별 표준 UPM 없음(공정 표준 사용), 셋업(5) 기록 없음, 대기 사유 없음 → Extension 후보. ProductionPerformanceEquipment는 완공·상태 이력에서 파생</t>
         </is>
       </c>
     </row>
@@ -69250,7 +69255,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Lot, OperationEnd, ItemMaster, Operation</t>
+          <t>Lot, OperationEnd, ItemMaster, Operation, GoodsIssue, StandardCost*</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -69267,7 +69272,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>D-PORO(기공) 표준 상세코드 없음 → Extension 후보. 검사 판정(judge) 표준 속성 없음 → Extension 후보</t>
+          <t>D-PORO(기공) 표준 상세코드 없음 → Extension 후보. 검사 판정(judge) 표준 속성 없음 → Extension 후보. KPI(PR04·QM06): 불량금액은 QMS 폐기 × 공정 단계 원가로 산출 → 공정 단계 원가(StandardCost) Extension 필요</t>
         </is>
       </c>
     </row>

--- a/mapping/impix/s1/S1_원천인벤토리_IMPIX.xlsx
+++ b/mapping/impix/s1/S1_원천인벤토리_IMPIX.xlsx
@@ -531,7 +531,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22 17:46</t>
+          <t>2026-10-22 17:58</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>SC05, SC06, SC07</t>
+          <t>SC02, SC05, SC06, SC07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>SC07</t>
+          <t>SC07, SC02</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -69149,9 +69149,11 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>erp.tb_hr_emp
+          <t>erp.tb_co_std_cost
+erp.tb_hr_emp
 erp.tb_mm_item
 erp.tb_pp_mo
+erp.tb_pp_plan
 erp.tb_pp_rcpt
 mes.tb_lot
 mes.tb_lot_link
